--- a/src/Verify.OpenXml.Tests/ExcelDocumentPropertiesTests.DocumentProperties.verified.xlsx
+++ b/src/Verify.OpenXml.Tests/ExcelDocumentPropertiesTests.DocumentProperties.verified.xlsx
@@ -18,5 +18,6 @@
       </c>
     </row>
   </sheetData>
+  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
--- a/src/Verify.OpenXml.Tests/ExcelDocumentPropertiesTests.DocumentProperties.verified.xlsx
+++ b/src/Verify.OpenXml.Tests/ExcelDocumentPropertiesTests.DocumentProperties.verified.xlsx
@@ -18,6 +18,5 @@
       </c>
     </row>
   </sheetData>
-  <pageSetup paperSize="9"/>
 </worksheet>
 </file>